--- a/originales/respuestas/2025/01. Calificadas/bucle p12/Unidad Administrativa Especial De Rehabilitación Y Mantenimiento Vial.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p12/Unidad Administrativa Especial De Rehabilitación Y Mantenimiento Vial.xlsx
@@ -449,7 +449,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="23.43"/>
-    <col customWidth="1" min="2" max="2" width="65.29"/>
+    <col customWidth="1" min="2" max="2" width="77.57"/>
     <col customWidth="1" min="3" max="3" width="32.43"/>
     <col customWidth="1" min="4" max="4" width="29.86"/>
     <col customWidth="1" min="5" max="5" width="32.0"/>
